--- a/Analysis/Phase2TableSummaryWeb.xlsx
+++ b/Analysis/Phase2TableSummaryWeb.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/VulnEnvLLM/Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3585912C-33DE-4D41-8E60-6FB799C35441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAA18EB-D653-1446-A456-C6EFC55DF8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-3420" windowWidth="38400" windowHeight="21100" xr2:uid="{BCC9BDAD-BCD6-5440-87F9-CBF79B9E5125}"/>
+    <workbookView xWindow="38400" yWindow="-1440" windowWidth="21600" windowHeight="21100" xr2:uid="{BCC9BDAD-BCD6-5440-87F9-CBF79B9E5125}"/>
   </bookViews>
   <sheets>
     <sheet name="Web" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>CVE-ID</t>
   </si>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t>Exploit</t>
+  </si>
+  <si>
+    <t>CVE-2016-7982</t>
+  </si>
+  <si>
+    <t>CVE-2019-16278</t>
   </si>
 </sst>
 </file>
@@ -449,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{782401BC-52A7-914C-A953-72BD0B4A7357}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -673,6 +679,74 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Analysis/Phase2TableSummaryWeb.xlsx
+++ b/Analysis/Phase2TableSummaryWeb.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAA18EB-D653-1446-A456-C6EFC55DF8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9479C9E4-BA17-E240-9790-462931B2F3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="-1440" windowWidth="21600" windowHeight="21100" xr2:uid="{BCC9BDAD-BCD6-5440-87F9-CBF79B9E5125}"/>
+    <workbookView xWindow="38400" yWindow="500" windowWidth="21600" windowHeight="21100" xr2:uid="{BCC9BDAD-BCD6-5440-87F9-CBF79B9E5125}"/>
   </bookViews>
   <sheets>
     <sheet name="Web" sheetId="1" r:id="rId1"/>
@@ -457,6 +457,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{782401BC-52A7-914C-A953-72BD0B4A7357}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -676,7 +679,7 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
